--- a/output/price_predictions.xlsx
+++ b/output/price_predictions.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.000000"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -61,13 +63,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -434,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T4"/>
+  <dimension ref="A1:Y4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -452,11 +455,16 @@
     <col width="18" customWidth="1" min="13" max="13"/>
     <col width="21" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
-    <col width="10" customWidth="1" min="16" max="16"/>
-    <col width="11" customWidth="1" min="17" max="17"/>
-    <col width="11" customWidth="1" min="18" max="18"/>
-    <col width="22" customWidth="1" min="19" max="19"/>
-    <col width="10" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="19" customWidth="1" min="18" max="18"/>
+    <col width="19" customWidth="1" min="19" max="19"/>
+    <col width="23" customWidth="1" min="20" max="20"/>
+    <col width="10" customWidth="1" min="21" max="21"/>
+    <col width="11" customWidth="1" min="22" max="22"/>
+    <col width="12" customWidth="1" min="23" max="23"/>
+    <col width="21" customWidth="1" min="24" max="24"/>
+    <col width="10" customWidth="1" min="25" max="25"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -537,25 +545,50 @@
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
+          <t>station_name</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>station_line</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>station_latitude</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>station_longitude</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>station_lookup_status</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
           <t>AI予測㎡単価</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>AI予測成約価格</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>売出価格との差額</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>価格乖離率</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>価格評価</t>
         </is>
@@ -623,19 +656,40 @@
       <c r="O2" s="3" t="n">
         <v>45000000</v>
       </c>
-      <c r="P2" s="3" t="n">
-        <v>856766</v>
-      </c>
-      <c r="Q2" s="3" t="n">
-        <v>55861147</v>
-      </c>
-      <c r="R2" s="3" t="n">
-        <v>-10861147</v>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>北千住</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>常磐線</t>
+        </is>
+      </c>
+      <c r="R2" s="4" t="n">
+        <v>35.74929865138866</v>
       </c>
       <c r="S2" s="4" t="n">
-        <v>-0.1944311490775512</v>
+        <v>139.8050594329834</v>
       </c>
       <c r="T2" s="2" t="inlineStr">
+        <is>
+          <t>自動補完</t>
+        </is>
+      </c>
+      <c r="U2" s="3" t="n">
+        <v>1141896</v>
+      </c>
+      <c r="V2" s="3" t="n">
+        <v>74451592</v>
+      </c>
+      <c r="W2" s="3" t="n">
+        <v>-29451592</v>
+      </c>
+      <c r="X2" s="5" t="n">
+        <v>-0.3955804195563743</v>
+      </c>
+      <c r="Y2" s="2" t="inlineStr">
         <is>
           <t>割安</t>
         </is>
@@ -703,21 +757,42 @@
       <c r="O3" s="3" t="n">
         <v>60000000</v>
       </c>
-      <c r="P3" s="3" t="n">
-        <v>1065476</v>
-      </c>
-      <c r="Q3" s="3" t="n">
-        <v>58601201</v>
-      </c>
-      <c r="R3" s="3" t="n">
-        <v>1398799</v>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>三軒茶屋</t>
+        </is>
+      </c>
+      <c r="Q3" s="2" t="inlineStr">
+        <is>
+          <t>田園都市線</t>
+        </is>
+      </c>
+      <c r="R3" s="4" t="n">
+        <v>35.64366111008705</v>
       </c>
       <c r="S3" s="4" t="n">
-        <v>0.0238698008936711</v>
+        <v>139.6712923049927</v>
       </c>
       <c r="T3" s="2" t="inlineStr">
         <is>
-          <t>適正</t>
+          <t>自動補完</t>
+        </is>
+      </c>
+      <c r="U3" s="3" t="n">
+        <v>1929731</v>
+      </c>
+      <c r="V3" s="3" t="n">
+        <v>106135213</v>
+      </c>
+      <c r="W3" s="3" t="n">
+        <v>-46135213</v>
+      </c>
+      <c r="X3" s="5" t="n">
+        <v>-0.4346833788329986</v>
+      </c>
+      <c r="Y3" s="2" t="inlineStr">
+        <is>
+          <t>割安</t>
         </is>
       </c>
     </row>
@@ -783,21 +858,42 @@
       <c r="O4" s="3" t="n">
         <v>120000000</v>
       </c>
-      <c r="P4" s="3" t="n">
-        <v>1886493</v>
-      </c>
-      <c r="Q4" s="3" t="n">
-        <v>132054525</v>
-      </c>
-      <c r="R4" s="3" t="n">
-        <v>-12054525</v>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>六本木</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>2号線日比谷線</t>
+        </is>
+      </c>
+      <c r="R4" s="4" t="n">
+        <v>35.66329357678096</v>
       </c>
       <c r="S4" s="4" t="n">
-        <v>-0.09128445238813286</v>
+        <v>139.7321462631226</v>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>適正</t>
+          <t>自動補完</t>
+        </is>
+      </c>
+      <c r="U4" s="3" t="n">
+        <v>3352490</v>
+      </c>
+      <c r="V4" s="3" t="n">
+        <v>234674334</v>
+      </c>
+      <c r="W4" s="3" t="n">
+        <v>-114674334</v>
+      </c>
+      <c r="X4" s="5" t="n">
+        <v>-0.4886530710256538</v>
+      </c>
+      <c r="Y4" s="2" t="inlineStr">
+        <is>
+          <t>割安</t>
         </is>
       </c>
     </row>
@@ -812,11 +908,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -851,7 +947,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>5.0</t>
         </is>
       </c>
     </row>
@@ -863,7 +959,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>name_compact</t>
+          <t>station_geo_line</t>
         </is>
       </c>
     </row>
@@ -874,7 +970,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>17.70703826267798</v>
+        <v>17.26282128186162</v>
       </c>
     </row>
     <row r="6">
@@ -884,7 +980,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>0.8528159309501149</v>
+        <v>0.8654882464799249</v>
       </c>
     </row>
     <row r="7">
@@ -894,7 +990,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>12485824.96978749</v>
+        <v>12168235.05137179</v>
       </c>
     </row>
     <row r="8">
@@ -904,7 +1000,63 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>19641774.93297648</v>
+        <v>19017664.94306778</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>駅なしMAPE</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>17.7606302526858</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>駅なしR²</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>0.8546483489640611</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>駅特徴量</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>station_name, station_line, station_latitude, station_longitude</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>最終テスト</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>2026年</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>注意</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>最寄駅自動推定はcity + district_name 内で学習データ上最頻の駅を使用</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/output/price_predictions.xlsx
+++ b/output/price_predictions.xlsx
@@ -674,7 +674,7 @@
       </c>
       <c r="T2" s="2" t="inlineStr">
         <is>
-          <t>自動補完</t>
+          <t>入力値使用</t>
         </is>
       </c>
       <c r="U2" s="3" t="n">
@@ -775,7 +775,7 @@
       </c>
       <c r="T3" s="2" t="inlineStr">
         <is>
-          <t>自動補完</t>
+          <t>入力値使用</t>
         </is>
       </c>
       <c r="U3" s="3" t="n">
@@ -876,7 +876,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>自動補完</t>
+          <t>入力値使用</t>
         </is>
       </c>
       <c r="U4" s="3" t="n">
